--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>100.9783491817628</v>
+        <v>94.72654046762884</v>
       </c>
       <c r="C2">
-        <v>135.4560813388034</v>
+        <v>131.7440356678852</v>
       </c>
       <c r="D2">
-        <v>151.1422510487182</v>
+        <v>148.2345030934112</v>
       </c>
       <c r="E2">
-        <v>154.5177559345036</v>
+        <v>156.132524081533</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>123.5842855201298</v>
+        <v>118.1753089179812</v>
       </c>
       <c r="C3">
-        <v>162.7249581578534</v>
+        <v>158.7526938108934</v>
       </c>
       <c r="D3">
-        <v>178.6129849689628</v>
+        <v>175.7004361084484</v>
       </c>
       <c r="E3">
-        <v>183.6099480267958</v>
+        <v>185.9889559210775</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>124.1497658991431</v>
+        <v>103.2940631100031</v>
       </c>
       <c r="C4">
-        <v>163.4286255781191</v>
+        <v>147.8585557520053</v>
       </c>
       <c r="D4">
-        <v>178.5603470830609</v>
+        <v>168.3568331346805</v>
       </c>
       <c r="E4">
-        <v>183.2495897909949</v>
+        <v>178.8084080837329</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>99.32408398615753</v>
+        <v>88.68178775961273</v>
       </c>
       <c r="C5">
-        <v>121.0823238774124</v>
+        <v>114.8114517912198</v>
       </c>
       <c r="D5">
-        <v>125.7917890917096</v>
+        <v>120.7087590389347</v>
       </c>
       <c r="E5">
-        <v>128.9923023518884</v>
+        <v>127.0603560451834</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>86.19538314603743</v>
+        <v>76.64087752733985</v>
       </c>
       <c r="C6">
-        <v>106.0356497729024</v>
+        <v>99.0506165109433</v>
       </c>
       <c r="D6">
-        <v>111.382216681319</v>
+        <v>106.4278641153051</v>
       </c>
       <c r="E6">
-        <v>112.8501361708423</v>
+        <v>110.9642725767895</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>9.962475285044091</v>
+        <v>8.556061872758615</v>
       </c>
       <c r="C7">
-        <v>11.6592721000854</v>
+        <v>10.72557743548773</v>
       </c>
       <c r="D7">
-        <v>12.00761230885085</v>
+        <v>11.4513880430713</v>
       </c>
       <c r="E7">
-        <v>11.99095024139929</v>
+        <v>11.84143087829951</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>218.551758958026</v>
+        <v>283.1203258808434</v>
       </c>
       <c r="C8">
-        <v>393.0622647891806</v>
+        <v>441.9203503285401</v>
       </c>
       <c r="D8">
-        <v>498.8420785229688</v>
+        <v>537.287261301503</v>
       </c>
       <c r="E8">
-        <v>590.9876762663656</v>
+        <v>599.2709413296016</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>116.2330519429543</v>
+        <v>115.7502609702506</v>
       </c>
       <c r="C9">
-        <v>145.6668159247763</v>
+        <v>143.5151943743134</v>
       </c>
       <c r="D9">
-        <v>156.4400948979797</v>
+        <v>151.612607300604</v>
       </c>
       <c r="E9">
-        <v>160.4073832053651</v>
+        <v>158.8511403311513</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>55.30312867448148</v>
+        <v>50.03574183604502</v>
       </c>
       <c r="C10">
-        <v>65.76169805307622</v>
+        <v>61.53381390148514</v>
       </c>
       <c r="D10">
-        <v>69.27124029934959</v>
+        <v>66.20840949863424</v>
       </c>
       <c r="E10">
-        <v>68.49521374618028</v>
+        <v>67.5656795564007</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>10.21749790210974</v>
+        <v>9.217870017468412</v>
       </c>
       <c r="C11">
-        <v>11.50014217737278</v>
+        <v>10.71019883711017</v>
       </c>
       <c r="D11">
-        <v>11.96321789381961</v>
+        <v>11.44193823086221</v>
       </c>
       <c r="E11">
-        <v>12.76260879837906</v>
+        <v>12.63740343921768</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>25.43048401039587</v>
+        <v>24.77331179975072</v>
       </c>
       <c r="C12">
-        <v>30.98221688994789</v>
+        <v>29.25540472405986</v>
       </c>
       <c r="D12">
-        <v>32.0177261213151</v>
+        <v>30.37595654121452</v>
       </c>
       <c r="E12">
-        <v>31.14953398634933</v>
+        <v>30.46952081442694</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>31.06973549375791</v>
+        <v>28.02784984031769</v>
       </c>
       <c r="C13">
-        <v>36.63995134046976</v>
+        <v>34.12210686605644</v>
       </c>
       <c r="D13">
-        <v>38.96844108194558</v>
+        <v>37.19404359333081</v>
       </c>
       <c r="E13">
-        <v>38.98690148093603</v>
+        <v>38.40936694258598</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>94.72654046762884</v>
+        <v>3.625896285842252</v>
       </c>
       <c r="C2">
-        <v>131.7440356678852</v>
+        <v>10.71602203997152</v>
       </c>
       <c r="D2">
-        <v>148.2345030934112</v>
+        <v>23.40544785685439</v>
       </c>
       <c r="E2">
-        <v>156.132524081533</v>
+        <v>37.53185675036851</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>118.1753089179812</v>
+        <v>39.5525523725488</v>
       </c>
       <c r="C3">
-        <v>158.7526938108934</v>
+        <v>98.09109536282847</v>
       </c>
       <c r="D3">
-        <v>175.7004361084484</v>
+        <v>131.9546132406306</v>
       </c>
       <c r="E3">
-        <v>185.9889559210775</v>
+        <v>154.9907966008979</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>103.2940631100031</v>
+        <v>3.922559358607711</v>
       </c>
       <c r="C4">
-        <v>147.8585557520053</v>
+        <v>10.56132541085753</v>
       </c>
       <c r="D4">
-        <v>168.3568331346805</v>
+        <v>19.17989238243195</v>
       </c>
       <c r="E4">
-        <v>178.8084080837329</v>
+        <v>26.29535412996072</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>88.68178775961273</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>114.8114517912198</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>120.7087590389347</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>127.0603560451834</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>76.64087752733985</v>
+        <v>25.72560923994624</v>
       </c>
       <c r="C6">
-        <v>99.0506165109433</v>
+        <v>42.25236088928351</v>
       </c>
       <c r="D6">
-        <v>106.4278641153051</v>
+        <v>41.67804468851107</v>
       </c>
       <c r="E6">
-        <v>110.9642725767895</v>
+        <v>35.9461728065656</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8.556061872758615</v>
+        <v>2.852020624252872</v>
       </c>
       <c r="C7">
-        <v>10.72557743548773</v>
+        <v>7.150384956991823</v>
       </c>
       <c r="D7">
-        <v>11.4513880430713</v>
+        <v>8.397684564918952</v>
       </c>
       <c r="E7">
-        <v>11.84143087829951</v>
+        <v>9.473144702639608</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>283.1203258808434</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>441.9203503285401</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>537.287261301503</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>599.2709413296016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>115.7502609702506</v>
+        <v>207.9009541698676</v>
       </c>
       <c r="C9">
-        <v>143.5151943743134</v>
+        <v>411.1328998259315</v>
       </c>
       <c r="D9">
-        <v>151.612607300604</v>
+        <v>590.2587915295359</v>
       </c>
       <c r="E9">
-        <v>158.8511403311513</v>
+        <v>759.7228450620281</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>50.03574183604502</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>61.53381390148514</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>66.20840949863424</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>67.5656795564007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>9.217870017468412</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>10.71019883711017</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>11.44193823086221</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>12.63740343921768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>24.77331179975072</v>
+        <v>304.2670859507844</v>
       </c>
       <c r="C12">
-        <v>29.25540472405986</v>
+        <v>390.5596530661992</v>
       </c>
       <c r="D12">
-        <v>30.37595654121452</v>
+        <v>343.2483089157241</v>
       </c>
       <c r="E12">
-        <v>30.46952081442694</v>
+        <v>265.6317199206451</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>28.02784984031769</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>34.12210686605644</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>37.19404359333081</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>38.40936694258598</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.625896285842252</v>
+        <v>12.25205553353762</v>
       </c>
       <c r="C2">
-        <v>10.71602203997152</v>
+        <v>17.03994712830132</v>
       </c>
       <c r="D2">
-        <v>23.40544785685439</v>
+        <v>19.17284590908791</v>
       </c>
       <c r="E2">
-        <v>37.53185675036851</v>
+        <v>20.19438634827014</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>39.5525523725488</v>
+        <v>74.97272653350537</v>
       </c>
       <c r="C3">
-        <v>98.09109536282847</v>
+        <v>100.7158128759538</v>
       </c>
       <c r="D3">
-        <v>131.9546132406306</v>
+        <v>111.4677919506755</v>
       </c>
       <c r="E3">
-        <v>154.9907966008979</v>
+        <v>117.9950300802762</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.922559358607711</v>
+        <v>9.568292161768706</v>
       </c>
       <c r="C4">
-        <v>10.56132541085753</v>
+        <v>13.69637148018576</v>
       </c>
       <c r="D4">
-        <v>19.17989238243195</v>
+        <v>15.59515927984409</v>
       </c>
       <c r="E4">
-        <v>26.29535412996072</v>
+        <v>16.56330516986158</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>25.72560923994624</v>
+        <v>28.3208846904881</v>
       </c>
       <c r="C6">
-        <v>42.25236088928351</v>
+        <v>36.60189156533981</v>
       </c>
       <c r="D6">
-        <v>41.67804468851107</v>
+        <v>39.3279848131863</v>
       </c>
       <c r="E6">
-        <v>35.9461728065656</v>
+        <v>41.00431088214111</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.852020624252872</v>
+        <v>5.418839186080456</v>
       </c>
       <c r="C7">
-        <v>7.150384956991823</v>
+        <v>6.792865709142233</v>
       </c>
       <c r="D7">
-        <v>8.397684564918952</v>
+        <v>7.252545760611822</v>
       </c>
       <c r="E7">
-        <v>9.473144702639608</v>
+        <v>7.499572889589689</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>207.9009541698676</v>
+        <v>386.0677590472642</v>
       </c>
       <c r="C9">
-        <v>411.1328998259315</v>
+        <v>478.6735599288539</v>
       </c>
       <c r="D9">
-        <v>590.2587915295359</v>
+        <v>505.6812749554042</v>
       </c>
       <c r="E9">
-        <v>759.7228450620281</v>
+        <v>529.8243239858621</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>304.2670859507844</v>
+        <v>283.0115683452534</v>
       </c>
       <c r="C12">
-        <v>390.5596530661992</v>
+        <v>334.2152248539751</v>
       </c>
       <c r="D12">
-        <v>343.2483089157241</v>
+        <v>347.0164655499508</v>
       </c>
       <c r="E12">
-        <v>265.6317199206451</v>
+        <v>348.085348544561</v>
       </c>
     </row>
     <row r="13" spans="1:5">
